--- a/public/plantilla-cierre.xlsx
+++ b/public/plantilla-cierre.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="7" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="7" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Financiero" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,6 +115,11 @@
       <i val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -311,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -334,53 +339,53 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -428,17 +433,17 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -451,7 +456,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -466,13 +471,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -502,10 +507,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -523,13 +528,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -539,58 +544,126 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -961,6 +1034,8 @@
     <col width="14" customWidth="1" style="37" min="5" max="5"/>
     <col width="19" customWidth="1" style="37" min="6" max="6"/>
     <col width="14" customWidth="1" style="37" min="7" max="9"/>
+    <col width="13" customWidth="1" style="37" min="8" max="8"/>
+    <col width="13" customWidth="1" style="37" min="9" max="9"/>
     <col width="15.77734375" customWidth="1" style="37" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -1091,8 +1166,8 @@
       </c>
       <c r="B10" s="100" t="n"/>
       <c r="C10" s="87" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="87" t="n"/>
+      <c r="D10" s="108" t="n"/>
+      <c r="E10" s="109" t="n"/>
       <c r="F10" s="25" t="inlineStr">
         <is>
           <t>Tipo de proyecto</t>
@@ -1100,8 +1175,8 @@
       </c>
       <c r="G10" s="100" t="n"/>
       <c r="H10" s="87" t="n"/>
-      <c r="I10" s="27" t="n"/>
-      <c r="J10" s="87" t="n"/>
+      <c r="I10" s="108" t="n"/>
+      <c r="J10" s="109" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="37">
       <c r="A11" s="25" t="inlineStr">
@@ -1111,8 +1186,8 @@
       </c>
       <c r="B11" s="100" t="n"/>
       <c r="C11" s="87" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="87" t="n"/>
+      <c r="D11" s="108" t="n"/>
+      <c r="E11" s="109" t="n"/>
       <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Contratante</t>
@@ -1120,8 +1195,8 @@
       </c>
       <c r="G11" s="100" t="n"/>
       <c r="H11" s="87" t="n"/>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="87" t="n"/>
+      <c r="I11" s="108" t="n"/>
+      <c r="J11" s="109" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="37">
       <c r="A12" s="25" t="inlineStr">
@@ -1131,8 +1206,8 @@
       </c>
       <c r="B12" s="100" t="n"/>
       <c r="C12" s="87" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="87" t="n"/>
+      <c r="D12" s="108" t="n"/>
+      <c r="E12" s="109" t="n"/>
       <c r="F12" s="25" t="inlineStr">
         <is>
           <t>Responsable del cierre</t>
@@ -1140,8 +1215,8 @@
       </c>
       <c r="G12" s="100" t="n"/>
       <c r="H12" s="87" t="n"/>
-      <c r="I12" s="27" t="n"/>
-      <c r="J12" s="87" t="n"/>
+      <c r="I12" s="108" t="n"/>
+      <c r="J12" s="109" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="37">
       <c r="A13" s="43" t="inlineStr">
@@ -1159,7 +1234,7 @@
       <c r="I13" s="100" t="n"/>
       <c r="J13" s="87" t="n"/>
     </row>
-    <row r="14" ht="18" customHeight="1" s="37">
+    <row r="14" ht="42" customHeight="1" s="37">
       <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Valor del contrato inicial</t>
@@ -1167,8 +1242,8 @@
       </c>
       <c r="B14" s="100" t="n"/>
       <c r="C14" s="87" t="n"/>
-      <c r="D14" s="47" t="n"/>
-      <c r="F14" s="27" t="inlineStr">
+      <c r="D14" s="110" t="n"/>
+      <c r="F14" s="111" t="inlineStr">
         <is>
           <t>Los deductivos se escriben como valor positivo; el formato los resta.
 Saldo por facturar: lo que falta cobrar del valor final. Debe quedar en cero al liquidar el contrato.</t>
@@ -1187,7 +1262,7 @@
       </c>
       <c r="B15" s="100" t="n"/>
       <c r="C15" s="87" t="n"/>
-      <c r="D15" s="47" t="n"/>
+      <c r="D15" s="110" t="n"/>
       <c r="F15" s="52" t="n"/>
       <c r="J15" s="53" t="n"/>
     </row>
@@ -1199,7 +1274,7 @@
       </c>
       <c r="B16" s="100" t="n"/>
       <c r="C16" s="87" t="n"/>
-      <c r="D16" s="47" t="n"/>
+      <c r="D16" s="110" t="n"/>
       <c r="F16" s="52" t="n"/>
       <c r="J16" s="53" t="n"/>
     </row>
@@ -1211,7 +1286,7 @@
       </c>
       <c r="B17" s="100" t="n"/>
       <c r="C17" s="87" t="n"/>
-      <c r="D17" s="98">
+      <c r="D17" s="112">
         <f>N(D14)+N(D15)-N(D16)</f>
         <v/>
       </c>
@@ -1226,7 +1301,7 @@
       </c>
       <c r="B18" s="100" t="n"/>
       <c r="C18" s="87" t="n"/>
-      <c r="D18" s="47" t="n"/>
+      <c r="D18" s="110" t="n"/>
       <c r="F18" s="52" t="n"/>
       <c r="J18" s="53" t="n"/>
     </row>
@@ -1238,7 +1313,7 @@
       </c>
       <c r="B19" s="100" t="n"/>
       <c r="C19" s="87" t="n"/>
-      <c r="D19" s="98">
+      <c r="D19" s="112">
         <f>D17-N(D18)</f>
         <v/>
       </c>
@@ -1293,8 +1368,8 @@
       <c r="I22" s="105" t="n"/>
       <c r="J22" s="105" t="n"/>
     </row>
-    <row r="23" ht="19.95" customHeight="1" s="37">
-      <c r="A23" s="6" t="n">
+    <row r="23" ht="29" customHeight="1" s="37">
+      <c r="A23" s="113" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="25" t="inlineStr">
@@ -1302,12 +1377,12 @@
           <t>Material</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="101">
+      <c r="C23" s="110" t="n"/>
+      <c r="D23" s="114">
         <f>IF(OR(C23="",C30=0),"",C23/C30)</f>
         <v/>
       </c>
-      <c r="F23" s="27" t="inlineStr">
+      <c r="F23" s="111" t="inlineStr">
         <is>
           <t>El costo real final es la suma de todo lo registrado en la obra (Registro de Costos), con IVA.</t>
         </is>
@@ -1318,7 +1393,7 @@
       <c r="J23" s="51" t="n"/>
     </row>
     <row r="24" ht="19.95" customHeight="1" s="37">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="113" t="n">
         <v>2</v>
       </c>
       <c r="B24" s="25" t="inlineStr">
@@ -1326,8 +1401,8 @@
           <t>Mano de obra</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="101">
+      <c r="C24" s="110" t="n"/>
+      <c r="D24" s="114">
         <f>IF(OR(C24="",C30=0),"",C24/C30)</f>
         <v/>
       </c>
@@ -1335,7 +1410,7 @@
       <c r="J24" s="53" t="n"/>
     </row>
     <row r="25" ht="19.95" customHeight="1" s="37">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="113" t="n">
         <v>3</v>
       </c>
       <c r="B25" s="25" t="inlineStr">
@@ -1343,8 +1418,8 @@
           <t>Subcontrato</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="101">
+      <c r="C25" s="110" t="n"/>
+      <c r="D25" s="114">
         <f>IF(OR(C25="",C30=0),"",C25/C30)</f>
         <v/>
       </c>
@@ -1352,7 +1427,7 @@
       <c r="J25" s="53" t="n"/>
     </row>
     <row r="26" ht="19.95" customHeight="1" s="37">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="113" t="n">
         <v>4</v>
       </c>
       <c r="B26" s="25" t="inlineStr">
@@ -1360,8 +1435,8 @@
           <t>Maquinaria y equipo</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="101">
+      <c r="C26" s="110" t="n"/>
+      <c r="D26" s="114">
         <f>IF(OR(C26="",C30=0),"",C26/C30)</f>
         <v/>
       </c>
@@ -1369,7 +1444,7 @@
       <c r="J26" s="53" t="n"/>
     </row>
     <row r="27" ht="19.95" customHeight="1" s="37">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="113" t="n">
         <v>5</v>
       </c>
       <c r="B27" s="25" t="inlineStr">
@@ -1377,8 +1452,8 @@
           <t>Transporte</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="101">
+      <c r="C27" s="110" t="n"/>
+      <c r="D27" s="114">
         <f>IF(OR(C27="",C30=0),"",C27/C30)</f>
         <v/>
       </c>
@@ -1386,7 +1461,7 @@
       <c r="J27" s="53" t="n"/>
     </row>
     <row r="28" ht="19.95" customHeight="1" s="37">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="113" t="n">
         <v>6</v>
       </c>
       <c r="B28" s="25" t="inlineStr">
@@ -1394,8 +1469,8 @@
           <t>Administración</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="101">
+      <c r="C28" s="110" t="n"/>
+      <c r="D28" s="114">
         <f>IF(OR(C28="",C30=0),"",C28/C30)</f>
         <v/>
       </c>
@@ -1403,7 +1478,7 @@
       <c r="J28" s="53" t="n"/>
     </row>
     <row r="29" ht="19.95" customHeight="1" s="37">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="113" t="n">
         <v>7</v>
       </c>
       <c r="B29" s="25" t="inlineStr">
@@ -1411,8 +1486,8 @@
           <t>Otro</t>
         </is>
       </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="101">
+      <c r="C29" s="110" t="n"/>
+      <c r="D29" s="114">
         <f>IF(OR(C29="",C30=0),"",C29/C30)</f>
         <v/>
       </c>
@@ -1426,11 +1501,11 @@
         </is>
       </c>
       <c r="B30" s="87" t="n"/>
-      <c r="C30" s="89">
+      <c r="C30" s="115">
         <f>SUM(C23:C29)</f>
         <v/>
       </c>
-      <c r="D30" s="85">
+      <c r="D30" s="116">
         <f>IF(C30=0,"",1)</f>
         <v/>
       </c>
@@ -1457,7 +1532,7 @@
       <c r="I32" s="100" t="n"/>
       <c r="J32" s="87" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1" s="37">
+    <row r="33" ht="42" customHeight="1" s="37">
       <c r="A33" s="25" t="inlineStr">
         <is>
           <t>Utilidad final (valor final − costo total)</t>
@@ -1465,11 +1540,11 @@
       </c>
       <c r="B33" s="100" t="n"/>
       <c r="C33" s="87" t="n"/>
-      <c r="D33" s="98">
+      <c r="D33" s="112">
         <f>IF(N(D17)=0,"",D17-C30)</f>
         <v/>
       </c>
-      <c r="F33" s="27" t="inlineStr">
+      <c r="F33" s="111" t="inlineStr">
         <is>
           <t>La utilidad pactada es la del AIU del contrato (la «U»).
 POR DEBAJO DE LO PACTADO: la obra dejó utilidad, pero menos de lo previsto.</t>
@@ -1488,7 +1563,7 @@
       </c>
       <c r="B34" s="100" t="n"/>
       <c r="C34" s="87" t="n"/>
-      <c r="D34" s="99">
+      <c r="D34" s="117">
         <f>IF(D33="","",D33/D17)</f>
         <v/>
       </c>
@@ -1503,7 +1578,7 @@
       </c>
       <c r="B35" s="100" t="n"/>
       <c r="C35" s="87" t="n"/>
-      <c r="D35" s="48" t="n"/>
+      <c r="D35" s="118" t="n"/>
       <c r="F35" s="52" t="n"/>
       <c r="J35" s="53" t="n"/>
     </row>
@@ -1515,7 +1590,7 @@
       </c>
       <c r="B36" s="100" t="n"/>
       <c r="C36" s="87" t="n"/>
-      <c r="D36" s="99">
+      <c r="D36" s="117">
         <f>IF(OR(D34="",D35=""),"",D34-D35)</f>
         <v/>
       </c>
@@ -1557,7 +1632,7 @@
       <c r="I39" s="100" t="n"/>
       <c r="J39" s="87" t="n"/>
     </row>
-    <row r="40" ht="18" customHeight="1" s="37">
+    <row r="40" ht="68" customHeight="1" s="37">
       <c r="A40" s="25" t="inlineStr">
         <is>
           <t>Unidad de medida</t>
@@ -1565,8 +1640,8 @@
       </c>
       <c r="B40" s="100" t="n"/>
       <c r="C40" s="87" t="n"/>
-      <c r="D40" s="106" t="n"/>
-      <c r="F40" s="27" t="inlineStr">
+      <c r="D40" s="119" t="n"/>
+      <c r="F40" s="111" t="inlineStr">
         <is>
           <t>Unidad según el tipo de proyecto:
   Edificación / Reformas → m² construidos.
@@ -1588,7 +1663,7 @@
       </c>
       <c r="B41" s="100" t="n"/>
       <c r="C41" s="87" t="n"/>
-      <c r="D41" s="107" t="n"/>
+      <c r="D41" s="120" t="n"/>
       <c r="F41" s="52" t="n"/>
       <c r="J41" s="53" t="n"/>
     </row>
@@ -1600,7 +1675,7 @@
       </c>
       <c r="B42" s="100" t="n"/>
       <c r="C42" s="87" t="n"/>
-      <c r="D42" s="98">
+      <c r="D42" s="112">
         <f>IF(N(D41)=0,"",C30/D41)</f>
         <v/>
       </c>
@@ -1615,7 +1690,7 @@
       </c>
       <c r="B43" s="100" t="n"/>
       <c r="C43" s="87" t="n"/>
-      <c r="D43" s="98">
+      <c r="D43" s="112">
         <f>IF(N(D41)=0,"",D17/D41)</f>
         <v/>
       </c>
@@ -1630,7 +1705,7 @@
       </c>
       <c r="B44" s="100" t="n"/>
       <c r="C44" s="87" t="n"/>
-      <c r="D44" s="98">
+      <c r="D44" s="112">
         <f>IF(D42="","",D43-D42)</f>
         <v/>
       </c>
@@ -1657,7 +1732,7 @@
       <c r="I46" s="100" t="n"/>
       <c r="J46" s="87" t="n"/>
     </row>
-    <row r="47" ht="18" customHeight="1" s="37">
+    <row r="47" ht="55" customHeight="1" s="37">
       <c r="A47" s="25" t="inlineStr">
         <is>
           <t>Anticipo entregado</t>
@@ -1665,8 +1740,8 @@
       </c>
       <c r="B47" s="100" t="n"/>
       <c r="C47" s="87" t="n"/>
-      <c r="D47" s="47" t="n"/>
-      <c r="F47" s="27" t="inlineStr">
+      <c r="D47" s="110" t="n"/>
+      <c r="F47" s="111" t="inlineStr">
         <is>
           <t>Anticipo sin amortizar y retegarantía: deben quedar resueltos en el acta de liquidación.
 Cuentas por pagar: proveedores y subcontratistas que aún no se han pagado (ver formato de Cuentas por Pagar).</t>
@@ -1685,7 +1760,7 @@
       </c>
       <c r="B48" s="100" t="n"/>
       <c r="C48" s="87" t="n"/>
-      <c r="D48" s="47" t="n"/>
+      <c r="D48" s="110" t="n"/>
       <c r="F48" s="52" t="n"/>
       <c r="J48" s="53" t="n"/>
     </row>
@@ -1697,7 +1772,7 @@
       </c>
       <c r="B49" s="100" t="n"/>
       <c r="C49" s="87" t="n"/>
-      <c r="D49" s="98">
+      <c r="D49" s="112">
         <f>N(D47)-N(D48)</f>
         <v/>
       </c>
@@ -1712,7 +1787,7 @@
       </c>
       <c r="B50" s="100" t="n"/>
       <c r="C50" s="87" t="n"/>
-      <c r="D50" s="47" t="n"/>
+      <c r="D50" s="110" t="n"/>
       <c r="F50" s="52" t="n"/>
       <c r="J50" s="53" t="n"/>
     </row>
@@ -1724,7 +1799,7 @@
       </c>
       <c r="B51" s="100" t="n"/>
       <c r="C51" s="87" t="n"/>
-      <c r="D51" s="47" t="n"/>
+      <c r="D51" s="110" t="n"/>
       <c r="F51" s="54" t="n"/>
       <c r="G51" s="55" t="n"/>
       <c r="H51" s="55" t="n"/>
@@ -1749,36 +1824,52 @@
       <c r="J53" s="87" t="n"/>
     </row>
     <row r="54" ht="22.05" customHeight="1" s="37">
-      <c r="A54" s="27" t="n"/>
-      <c r="B54" s="50" t="n"/>
-      <c r="C54" s="50" t="n"/>
-      <c r="D54" s="50" t="n"/>
-      <c r="E54" s="50" t="n"/>
-      <c r="F54" s="50" t="n"/>
-      <c r="G54" s="50" t="n"/>
-      <c r="H54" s="50" t="n"/>
-      <c r="I54" s="50" t="n"/>
-      <c r="J54" s="51" t="n"/>
+      <c r="A54" s="108" t="n"/>
+      <c r="B54" s="121" t="n"/>
+      <c r="C54" s="121" t="n"/>
+      <c r="D54" s="121" t="n"/>
+      <c r="E54" s="121" t="n"/>
+      <c r="F54" s="121" t="n"/>
+      <c r="G54" s="121" t="n"/>
+      <c r="H54" s="121" t="n"/>
+      <c r="I54" s="121" t="n"/>
+      <c r="J54" s="122" t="n"/>
     </row>
     <row r="55" ht="22.05" customHeight="1" s="37">
-      <c r="A55" s="52" t="n"/>
-      <c r="J55" s="53" t="n"/>
+      <c r="A55" s="123" t="n"/>
+      <c r="B55" s="124" t="n"/>
+      <c r="C55" s="124" t="n"/>
+      <c r="D55" s="124" t="n"/>
+      <c r="E55" s="124" t="n"/>
+      <c r="F55" s="124" t="n"/>
+      <c r="G55" s="124" t="n"/>
+      <c r="H55" s="124" t="n"/>
+      <c r="I55" s="124" t="n"/>
+      <c r="J55" s="125" t="n"/>
     </row>
     <row r="56" ht="22.05" customHeight="1" s="37">
-      <c r="A56" s="52" t="n"/>
-      <c r="J56" s="53" t="n"/>
+      <c r="A56" s="123" t="n"/>
+      <c r="B56" s="124" t="n"/>
+      <c r="C56" s="124" t="n"/>
+      <c r="D56" s="124" t="n"/>
+      <c r="E56" s="124" t="n"/>
+      <c r="F56" s="124" t="n"/>
+      <c r="G56" s="124" t="n"/>
+      <c r="H56" s="124" t="n"/>
+      <c r="I56" s="124" t="n"/>
+      <c r="J56" s="125" t="n"/>
     </row>
     <row r="57" ht="22.05" customHeight="1" s="37">
-      <c r="A57" s="54" t="n"/>
-      <c r="B57" s="55" t="n"/>
-      <c r="C57" s="55" t="n"/>
-      <c r="D57" s="55" t="n"/>
-      <c r="E57" s="55" t="n"/>
-      <c r="F57" s="55" t="n"/>
-      <c r="G57" s="55" t="n"/>
-      <c r="H57" s="55" t="n"/>
-      <c r="I57" s="55" t="n"/>
-      <c r="J57" s="56" t="n"/>
+      <c r="A57" s="126" t="n"/>
+      <c r="B57" s="127" t="n"/>
+      <c r="C57" s="127" t="n"/>
+      <c r="D57" s="127" t="n"/>
+      <c r="E57" s="127" t="n"/>
+      <c r="F57" s="127" t="n"/>
+      <c r="G57" s="127" t="n"/>
+      <c r="H57" s="127" t="n"/>
+      <c r="I57" s="127" t="n"/>
+      <c r="J57" s="128" t="n"/>
     </row>
     <row r="58"/>
     <row r="59" ht="15" customHeight="1" s="37">
@@ -1825,8 +1916,8 @@
       </c>
       <c r="B61" s="100" t="n"/>
       <c r="C61" s="87" t="n"/>
-      <c r="D61" s="27" t="n"/>
-      <c r="E61" s="87" t="n"/>
+      <c r="D61" s="108" t="n"/>
+      <c r="E61" s="109" t="n"/>
       <c r="F61" s="25" t="inlineStr">
         <is>
           <t>Firma:</t>
@@ -1834,8 +1925,8 @@
       </c>
       <c r="G61" s="100" t="n"/>
       <c r="H61" s="87" t="n"/>
-      <c r="I61" s="27" t="n"/>
-      <c r="J61" s="87" t="n"/>
+      <c r="I61" s="108" t="n"/>
+      <c r="J61" s="109" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1" s="37">
       <c r="A62" s="25" t="inlineStr">
@@ -1845,8 +1936,8 @@
       </c>
       <c r="B62" s="100" t="n"/>
       <c r="C62" s="87" t="n"/>
-      <c r="D62" s="27" t="n"/>
-      <c r="E62" s="87" t="n"/>
+      <c r="D62" s="108" t="n"/>
+      <c r="E62" s="109" t="n"/>
       <c r="F62" s="25" t="inlineStr">
         <is>
           <t>Nombre:</t>
@@ -1854,8 +1945,8 @@
       </c>
       <c r="G62" s="100" t="n"/>
       <c r="H62" s="87" t="n"/>
-      <c r="I62" s="27" t="n"/>
-      <c r="J62" s="87" t="n"/>
+      <c r="I62" s="108" t="n"/>
+      <c r="J62" s="109" t="n"/>
     </row>
     <row r="63" ht="15" customHeight="1" s="37">
       <c r="A63" s="25" t="inlineStr">
@@ -1865,8 +1956,8 @@
       </c>
       <c r="B63" s="100" t="n"/>
       <c r="C63" s="87" t="n"/>
-      <c r="D63" s="27" t="n"/>
-      <c r="E63" s="87" t="n"/>
+      <c r="D63" s="108" t="n"/>
+      <c r="E63" s="109" t="n"/>
       <c r="F63" s="25" t="inlineStr">
         <is>
           <t>Cargo:</t>
@@ -1874,10 +1965,11 @@
       </c>
       <c r="G63" s="100" t="n"/>
       <c r="H63" s="87" t="n"/>
-      <c r="I63" s="27" t="n"/>
-      <c r="J63" s="87" t="n"/>
+      <c r="I63" s="108" t="n"/>
+      <c r="J63" s="109" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="76">
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A32:J32"/>
